--- a/InputData/elec/CSC/Capacity Supply Curve.xlsx
+++ b/InputData/elec/CSC/Capacity Supply Curve.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\CSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\MA\elec\CSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8248DB4-6E2E-435A-8D3A-C7FBE3A7900C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E71632E-BF84-4D38-A349-FCC0A2AB5877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13575" yWindow="10755" windowWidth="21840" windowHeight="9120" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
+    <workbookView xWindow="13650" yWindow="1050" windowWidth="13545" windowHeight="16185" firstSheet="2" activeTab="3" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">Source: </t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>CSC Capacity Supply Curve Share of Cost Effective Capacity Built in a Single Year</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
   </si>
 </sst>
 </file>
@@ -184,9 +187,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -501,25 +505,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3D2DEE-686E-48A0-AC3D-0F54DEA5D0EC}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="2">
+        <v>45267</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -527,7 +537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -1262,94 +1272,94 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="C7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="D7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="E7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="F7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="G7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="H7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="I7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="J7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="K7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="L7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="M7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="N7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="O7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="P7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="Q7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="R7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="S7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="T7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="U7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="V7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="X7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="Y7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="Z7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="AA7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="AB7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="AC7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="AE7">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">

--- a/InputData/elec/CSC/Capacity Supply Curve.xlsx
+++ b/InputData/elec/CSC/Capacity Supply Curve.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\MA\elec\CSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\CSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E71632E-BF84-4D38-A349-FCC0A2AB5877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B22D3C2-F9E7-4EEF-AC87-E83AA2134C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13650" yWindow="1050" windowWidth="13545" windowHeight="16185" firstSheet="2" activeTab="3" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">Source: </t>
   </si>
@@ -141,9 +141,6 @@
   </si>
   <si>
     <t>CSC Capacity Supply Curve Share of Cost Effective Capacity Built in a Single Year</t>
-  </si>
-  <si>
-    <t>Massachusetts</t>
   </si>
 </sst>
 </file>
@@ -187,10 +184,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,31 +501,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3D2DEE-686E-48A0-AC3D-0F54DEA5D0EC}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="2">
-        <v>45267</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -537,7 +527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
